--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_FLANIGAN CALVIÀ.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_FLANIGAN CALVIÀ.xlsx
@@ -565,13 +565,13 @@
         <v>23</v>
       </c>
       <c r="D2" t="n">
-        <v>64.5119</v>
+        <v>60.2432</v>
       </c>
       <c r="E2" t="n">
-        <v>69.2196</v>
+        <v>62.2587</v>
       </c>
       <c r="F2" t="n">
-        <v>-4.7077</v>
+        <v>-2.0158</v>
       </c>
       <c r="G2" t="n">
         <v>31.3563</v>
@@ -610,13 +610,13 @@
         <v>53.5637</v>
       </c>
       <c r="S2" t="n">
-        <v>10.7135</v>
+        <v>6.4451</v>
       </c>
       <c r="T2" t="n">
-        <v>13.2212</v>
+        <v>6.2606</v>
       </c>
       <c r="U2" t="n">
-        <v>-2.5074</v>
+        <v>0.1845999999999999</v>
       </c>
       <c r="V2" t="n">
         <v>3.3971</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. ALMENTA MACIAS</t>
+          <t>R. VICENTE SIMO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>20.9678</v>
+        <v>13.7427</v>
       </c>
       <c r="E3" t="n">
-        <v>14.7572</v>
+        <v>15.5987</v>
       </c>
       <c r="F3" t="n">
-        <v>6.2102</v>
+        <v>-1.856099999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>-24.6513</v>
+        <v>-24.9536</v>
       </c>
       <c r="H3" t="n">
-        <v>-18.7046</v>
+        <v>-17.3429</v>
       </c>
       <c r="I3" t="n">
-        <v>-5.9469</v>
+        <v>-7.6109</v>
       </c>
       <c r="J3" t="n">
-        <v>27.8861</v>
+        <v>24.6342</v>
       </c>
       <c r="K3" t="n">
-        <v>17.3306</v>
+        <v>19.2147</v>
       </c>
       <c r="L3" t="n">
-        <v>10.5556</v>
+        <v>5.42</v>
       </c>
       <c r="M3" t="n">
-        <v>-52.5379</v>
+        <v>-49.5884</v>
       </c>
       <c r="N3" t="n">
-        <v>-36.0352</v>
+        <v>-36.558</v>
       </c>
       <c r="O3" t="n">
-        <v>-16.5025</v>
+        <v>-13.0305</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.0001999999999999225</v>
+        <v>25.9884</v>
       </c>
       <c r="Q3" t="n">
-        <v>-59.3168</v>
+        <v>-31.7413</v>
       </c>
       <c r="R3" t="n">
-        <v>59.3169</v>
+        <v>57.7298</v>
       </c>
       <c r="S3" t="n">
-        <v>32.7741</v>
+        <v>-1.0598</v>
       </c>
       <c r="T3" t="n">
-        <v>17.6655</v>
+        <v>-0.8531</v>
       </c>
       <c r="U3" t="n">
-        <v>15.1084</v>
+        <v>-0.2064999999999998</v>
       </c>
       <c r="V3" t="n">
-        <v>12.8454</v>
+        <v>13.768</v>
       </c>
       <c r="W3" t="n">
-        <v>28.5226</v>
+        <v>23.5589</v>
       </c>
       <c r="X3" t="n">
-        <v>-15.677</v>
+        <v>-9.7911</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>13</v>
       </c>
       <c r="D4" t="n">
-        <v>18.8897</v>
+        <v>5.820499999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>10.8383</v>
+        <v>-0.9236000000000009</v>
       </c>
       <c r="F4" t="n">
-        <v>8.0518</v>
+        <v>6.743999999999999</v>
       </c>
       <c r="G4" t="n">
         <v>-0.6357000000000004</v>
@@ -766,13 +766,13 @@
         <v>18.6482</v>
       </c>
       <c r="S4" t="n">
-        <v>21.6763</v>
+        <v>8.606999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>16.8303</v>
+        <v>5.0685</v>
       </c>
       <c r="U4" t="n">
-        <v>4.846</v>
+        <v>3.5385</v>
       </c>
       <c r="V4" t="n">
         <v>2.4118</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. AGUILA MULET</t>
+          <t>M. GARCIA CALVO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4275</v>
+        <v>5.662999999999998</v>
       </c>
       <c r="E5" t="n">
-        <v>1.3436</v>
+        <v>7.0636</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0839</v>
+        <v>-1.400599999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8619</v>
+        <v>3.9442</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8619</v>
+        <v>0.9253999999999989</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>3.018700000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9274</v>
+        <v>36.8649</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9274</v>
+        <v>23.315</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>13.55</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.06560000000000001</v>
+        <v>-32.9209</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.06560000000000001</v>
+        <v>-22.3898</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>-10.5313</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3968</v>
+        <v>-3.9677</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-39.875</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3968</v>
+        <v>35.9075</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1683</v>
+        <v>3.6094</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.187</v>
+        <v>0.6935</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0187</v>
+        <v>2.916</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3373</v>
+        <v>2.0774</v>
       </c>
       <c r="W5" t="n">
-        <v>0.6032</v>
+        <v>9.380800000000001</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.266</v>
+        <v>-7.303</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. GARCIA CALVO</t>
+          <t>A. ALMENTA MACIAS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.051600000000001</v>
+        <v>2.712600000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8003000000000005</v>
+        <v>4.458000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.8521</v>
+        <v>-1.745</v>
       </c>
       <c r="G6" t="n">
-        <v>3.9442</v>
+        <v>-24.6513</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9253999999999989</v>
+        <v>-18.7046</v>
       </c>
       <c r="I6" t="n">
-        <v>3.018700000000001</v>
+        <v>-5.9469</v>
       </c>
       <c r="J6" t="n">
-        <v>36.8649</v>
+        <v>27.8861</v>
       </c>
       <c r="K6" t="n">
-        <v>23.315</v>
+        <v>17.3306</v>
       </c>
       <c r="L6" t="n">
-        <v>13.55</v>
+        <v>10.5556</v>
       </c>
       <c r="M6" t="n">
-        <v>-32.9209</v>
+        <v>-52.5379</v>
       </c>
       <c r="N6" t="n">
-        <v>-22.3898</v>
+        <v>-36.0352</v>
       </c>
       <c r="O6" t="n">
-        <v>-10.5313</v>
+        <v>-16.5025</v>
       </c>
       <c r="P6" t="n">
-        <v>-3.9677</v>
+        <v>-0.0001999999999999225</v>
       </c>
       <c r="Q6" t="n">
-        <v>-39.875</v>
+        <v>-59.3168</v>
       </c>
       <c r="R6" t="n">
-        <v>35.9075</v>
+        <v>59.3169</v>
       </c>
       <c r="S6" t="n">
-        <v>-3.1055</v>
+        <v>14.5189</v>
       </c>
       <c r="T6" t="n">
-        <v>-5.569800000000001</v>
+        <v>7.366300000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>2.4645</v>
+        <v>7.1526</v>
       </c>
       <c r="V6" t="n">
-        <v>2.0774</v>
+        <v>12.8454</v>
       </c>
       <c r="W6" t="n">
-        <v>9.380800000000001</v>
+        <v>28.5226</v>
       </c>
       <c r="X6" t="n">
-        <v>-7.303</v>
+        <v>-15.677</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. SANTANDREU RODRIGUEZ</t>
+          <t>M. AGUILA MULET</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,67 +952,67 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.0862</v>
+        <v>1.5179</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6378999999999999</v>
+        <v>1.406</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.4482</v>
+        <v>0.112</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.1996</v>
+        <v>0.8619</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5143</v>
+        <v>0.8619</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.6853</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2317</v>
+        <v>0.9274</v>
       </c>
       <c r="K7" t="n">
-        <v>0.07099999999999995</v>
+        <v>0.9274</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.4313</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5853000000000002</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.846</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.9838</v>
+        <v>0.3968</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.3725</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3888</v>
+        <v>0.3968</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5816</v>
+        <v>-0.0779</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.442</v>
+        <v>-0.1247</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1396</v>
+        <v>0.0468</v>
       </c>
       <c r="V7" t="n">
-        <v>2.6789</v>
+        <v>0.3373</v>
       </c>
       <c r="W7" t="n">
-        <v>2.9449</v>
+        <v>0.6032</v>
       </c>
       <c r="X7" t="n">
         <v>-0.266</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. IDDRISU</t>
+          <t>J. GONZALEZ LOPEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="D8" t="n">
-        <v>-5.144900000000001</v>
+        <v>-1.290099999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.313099999999999</v>
+        <v>-5.5104</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.831700000000001</v>
+        <v>4.2203</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.513300000000001</v>
+        <v>13.1472</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.1181</v>
+        <v>6.4934</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.3949</v>
+        <v>6.654099999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>2.2401</v>
+        <v>33.5897</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9147000000000001</v>
+        <v>19.9735</v>
       </c>
       <c r="L8" t="n">
-        <v>1.3255</v>
+        <v>13.6163</v>
       </c>
       <c r="M8" t="n">
-        <v>-4.7532</v>
+        <v>-20.4423</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.0329</v>
+        <v>-13.4801</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.7204</v>
+        <v>-6.962</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.9839</v>
+        <v>-14.2835</v>
       </c>
       <c r="Q8" t="n">
-        <v>-8.927300000000001</v>
+        <v>-44.438</v>
       </c>
       <c r="R8" t="n">
-        <v>6.9436</v>
+        <v>30.1547</v>
       </c>
       <c r="S8" t="n">
-        <v>4.444</v>
+        <v>1.4129</v>
       </c>
       <c r="T8" t="n">
-        <v>3.7186</v>
+        <v>0.01850000000000004</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7252000000000001</v>
+        <v>1.3942</v>
       </c>
       <c r="V8" t="n">
-        <v>-5.0919</v>
+        <v>-1.5666</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6554</v>
+        <v>5.3198</v>
       </c>
       <c r="X8" t="n">
-        <v>-5.7473</v>
+        <v>-6.886299999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. VICENTE SIMO</t>
+          <t>M. SANTANDREU RODRIGUEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,70 +1108,70 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>-6.7736</v>
+        <v>-2.2612</v>
       </c>
       <c r="E9" t="n">
-        <v>1.819599999999999</v>
+        <v>-0.7570000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>-8.5931</v>
+        <v>-1.5042</v>
       </c>
       <c r="G9" t="n">
-        <v>-24.9536</v>
+        <v>-2.1996</v>
       </c>
       <c r="H9" t="n">
-        <v>-17.3429</v>
+        <v>-0.5143</v>
       </c>
       <c r="I9" t="n">
-        <v>-7.6109</v>
+        <v>-1.6853</v>
       </c>
       <c r="J9" t="n">
-        <v>24.6342</v>
+        <v>0.2317</v>
       </c>
       <c r="K9" t="n">
-        <v>19.2147</v>
+        <v>0.07099999999999995</v>
       </c>
       <c r="L9" t="n">
-        <v>5.42</v>
+        <v>0.1607</v>
       </c>
       <c r="M9" t="n">
-        <v>-49.5884</v>
+        <v>-2.4313</v>
       </c>
       <c r="N9" t="n">
-        <v>-36.558</v>
+        <v>-0.5853000000000002</v>
       </c>
       <c r="O9" t="n">
-        <v>-13.0305</v>
+        <v>-1.846</v>
       </c>
       <c r="P9" t="n">
-        <v>25.9884</v>
+        <v>-1.9838</v>
       </c>
       <c r="Q9" t="n">
-        <v>-31.7413</v>
+        <v>-3.3725</v>
       </c>
       <c r="R9" t="n">
-        <v>57.7298</v>
+        <v>1.3888</v>
       </c>
       <c r="S9" t="n">
-        <v>-21.5761</v>
+        <v>-0.7568</v>
       </c>
       <c r="T9" t="n">
-        <v>-14.6327</v>
+        <v>-0.5611</v>
       </c>
       <c r="U9" t="n">
-        <v>-6.9435</v>
+        <v>-0.1956</v>
       </c>
       <c r="V9" t="n">
-        <v>13.768</v>
+        <v>2.6789</v>
       </c>
       <c r="W9" t="n">
-        <v>23.5589</v>
+        <v>2.9449</v>
       </c>
       <c r="X9" t="n">
-        <v>-9.7911</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>26</v>
       </c>
       <c r="D10" t="n">
-        <v>-8.817400000000001</v>
+        <v>-4.544000000000002</v>
       </c>
       <c r="E10" t="n">
-        <v>8.2593</v>
+        <v>9.8691</v>
       </c>
       <c r="F10" t="n">
-        <v>-17.0767</v>
+        <v>-14.4131</v>
       </c>
       <c r="G10" t="n">
         <v>-16.3243</v>
@@ -1234,13 +1234,13 @@
         <v>43.0495</v>
       </c>
       <c r="S10" t="n">
-        <v>-6.833699999999999</v>
+        <v>-2.5602</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.2276</v>
+        <v>0.3819</v>
       </c>
       <c r="U10" t="n">
-        <v>-5.605700000000001</v>
+        <v>-2.9423</v>
       </c>
       <c r="V10" t="n">
         <v>-2.3236</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. GONZALEZ LOPEZ</t>
+          <t>A. IDDRISU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="D11" t="n">
-        <v>-13.3221</v>
+        <v>-6.8994</v>
       </c>
       <c r="E11" t="n">
-        <v>-13.5253</v>
+        <v>-4.3313</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2030999999999987</v>
+        <v>-2.5684</v>
       </c>
       <c r="G11" t="n">
-        <v>13.1472</v>
+        <v>-2.513300000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>6.4934</v>
+        <v>-1.1181</v>
       </c>
       <c r="I11" t="n">
-        <v>6.654099999999999</v>
+        <v>-1.3949</v>
       </c>
       <c r="J11" t="n">
-        <v>33.5897</v>
+        <v>2.2401</v>
       </c>
       <c r="K11" t="n">
-        <v>19.9735</v>
+        <v>0.9147000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>13.6163</v>
+        <v>1.3255</v>
       </c>
       <c r="M11" t="n">
-        <v>-20.4423</v>
+        <v>-4.7532</v>
       </c>
       <c r="N11" t="n">
-        <v>-13.4801</v>
+        <v>-2.0329</v>
       </c>
       <c r="O11" t="n">
-        <v>-6.962</v>
+        <v>-2.7204</v>
       </c>
       <c r="P11" t="n">
-        <v>-14.2835</v>
+        <v>-1.9839</v>
       </c>
       <c r="Q11" t="n">
-        <v>-44.438</v>
+        <v>-8.927300000000001</v>
       </c>
       <c r="R11" t="n">
-        <v>30.1547</v>
+        <v>6.9436</v>
       </c>
       <c r="S11" t="n">
-        <v>-10.619</v>
+        <v>2.6896</v>
       </c>
       <c r="T11" t="n">
-        <v>-7.9966</v>
+        <v>1.701</v>
       </c>
       <c r="U11" t="n">
-        <v>-2.6227</v>
+        <v>0.9887</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.5666</v>
+        <v>-5.0919</v>
       </c>
       <c r="W11" t="n">
-        <v>5.3198</v>
+        <v>0.6554</v>
       </c>
       <c r="X11" t="n">
-        <v>-6.886299999999999</v>
+        <v>-5.7473</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. BRADLEY MAYOL</t>
+          <t>A. MONTALBÁN PÉREZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D12" t="n">
-        <v>-20.0076</v>
+        <v>-10.6342</v>
       </c>
       <c r="E12" t="n">
-        <v>-15.7636</v>
+        <v>5.034800000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.2442</v>
+        <v>-15.6692</v>
       </c>
       <c r="G12" t="n">
-        <v>-19.9006</v>
+        <v>-13.188</v>
       </c>
       <c r="H12" t="n">
-        <v>-11.1656</v>
+        <v>-17.9628</v>
       </c>
       <c r="I12" t="n">
-        <v>-8.735100000000001</v>
+        <v>4.7751</v>
       </c>
       <c r="J12" t="n">
-        <v>-6.1837</v>
+        <v>13.6602</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.7169</v>
+        <v>2.5838</v>
       </c>
       <c r="L12" t="n">
-        <v>-4.466699999999999</v>
+        <v>11.0764</v>
       </c>
       <c r="M12" t="n">
-        <v>-13.717</v>
+        <v>-26.8478</v>
       </c>
       <c r="N12" t="n">
-        <v>-9.448700000000001</v>
+        <v>-20.5465</v>
       </c>
       <c r="O12" t="n">
-        <v>-4.2683</v>
+        <v>-6.301499999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>3.7693</v>
+        <v>10.7128</v>
       </c>
       <c r="Q12" t="n">
-        <v>-8.7288</v>
+        <v>-18.0527</v>
       </c>
       <c r="R12" t="n">
-        <v>12.4983</v>
+        <v>28.766</v>
       </c>
       <c r="S12" t="n">
-        <v>-6.2371</v>
+        <v>-3.4944</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.3234</v>
+        <v>-2.4757</v>
       </c>
       <c r="U12" t="n">
-        <v>-3.9139</v>
+        <v>-1.0184</v>
       </c>
       <c r="V12" t="n">
-        <v>2.3607</v>
+        <v>-4.6652</v>
       </c>
       <c r="W12" t="n">
-        <v>1.4724</v>
+        <v>11.9031</v>
       </c>
       <c r="X12" t="n">
-        <v>0.8883</v>
+        <v>-16.5684</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. MONTALBÁN PÉREZ</t>
+          <t>J. BRADLEY MAYOL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,70 +1420,70 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D13" t="n">
-        <v>-21.7648</v>
+        <v>-17.0043</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.608700000000002</v>
+        <v>-13.9212</v>
       </c>
       <c r="F13" t="n">
-        <v>-20.1566</v>
+        <v>-3.0828</v>
       </c>
       <c r="G13" t="n">
-        <v>-13.188</v>
+        <v>-19.9006</v>
       </c>
       <c r="H13" t="n">
-        <v>-17.9628</v>
+        <v>-11.1656</v>
       </c>
       <c r="I13" t="n">
-        <v>4.7751</v>
+        <v>-8.735100000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>13.6602</v>
+        <v>-6.1837</v>
       </c>
       <c r="K13" t="n">
-        <v>2.5838</v>
+        <v>-1.7169</v>
       </c>
       <c r="L13" t="n">
-        <v>11.0764</v>
+        <v>-4.466699999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>-26.8478</v>
+        <v>-13.717</v>
       </c>
       <c r="N13" t="n">
-        <v>-20.5465</v>
+        <v>-9.448700000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>-6.301499999999999</v>
+        <v>-4.2683</v>
       </c>
       <c r="P13" t="n">
-        <v>10.7128</v>
+        <v>3.7693</v>
       </c>
       <c r="Q13" t="n">
-        <v>-18.0527</v>
+        <v>-8.7288</v>
       </c>
       <c r="R13" t="n">
-        <v>28.766</v>
+        <v>12.4983</v>
       </c>
       <c r="S13" t="n">
-        <v>-14.6245</v>
+        <v>-3.2335</v>
       </c>
       <c r="T13" t="n">
-        <v>-9.118499999999999</v>
+        <v>-0.4813</v>
       </c>
       <c r="U13" t="n">
-        <v>-5.5056</v>
+        <v>-2.7522</v>
       </c>
       <c r="V13" t="n">
-        <v>-4.6652</v>
+        <v>2.3607</v>
       </c>
       <c r="W13" t="n">
-        <v>11.9031</v>
+        <v>1.4724</v>
       </c>
       <c r="X13" t="n">
-        <v>-16.5684</v>
+        <v>0.8883</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>24</v>
       </c>
       <c r="D14" t="n">
-        <v>-23.0145</v>
+        <v>-21.3743</v>
       </c>
       <c r="E14" t="n">
-        <v>-15.9462</v>
+        <v>-16.1561</v>
       </c>
       <c r="F14" t="n">
-        <v>-7.068099999999999</v>
+        <v>-5.218199999999999</v>
       </c>
       <c r="G14" t="n">
         <v>-12.2996</v>
@@ -1546,13 +1546,13 @@
         <v>35.7094</v>
       </c>
       <c r="S14" t="n">
-        <v>-4.111499999999999</v>
+        <v>-2.4711</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6896</v>
+        <v>-0.8994999999999997</v>
       </c>
       <c r="U14" t="n">
-        <v>-3.4215</v>
+        <v>-1.5715</v>
       </c>
       <c r="V14" t="n">
         <v>-8.1907</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. BENNASAR ROJO</t>
+          <t>D. POU BLINNIKOV</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D15" t="n">
-        <v>-30.9464</v>
+        <v>-28.2398</v>
       </c>
       <c r="E15" t="n">
-        <v>-19.933</v>
+        <v>-16.5688</v>
       </c>
       <c r="F15" t="n">
-        <v>-11.0131</v>
+        <v>-11.671</v>
       </c>
       <c r="G15" t="n">
-        <v>-23.7503</v>
+        <v>-7.2502</v>
       </c>
       <c r="H15" t="n">
-        <v>-15.2129</v>
+        <v>-15.2013</v>
       </c>
       <c r="I15" t="n">
-        <v>-8.5372</v>
+        <v>7.9513</v>
       </c>
       <c r="J15" t="n">
-        <v>-6.289700000000001</v>
+        <v>11.1473</v>
       </c>
       <c r="K15" t="n">
-        <v>-4.753900000000001</v>
+        <v>0.4509999999999998</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.5355</v>
+        <v>10.6964</v>
       </c>
       <c r="M15" t="n">
-        <v>-17.4602</v>
+        <v>-18.3974</v>
       </c>
       <c r="N15" t="n">
-        <v>-10.459</v>
+        <v>-15.652</v>
       </c>
       <c r="O15" t="n">
-        <v>-7.0015</v>
+        <v>-2.7455</v>
       </c>
       <c r="P15" t="n">
-        <v>3.3728</v>
+        <v>-9.1256</v>
       </c>
       <c r="Q15" t="n">
-        <v>-13.8867</v>
+        <v>-34.3203</v>
       </c>
       <c r="R15" t="n">
-        <v>17.2595</v>
+        <v>25.195</v>
       </c>
       <c r="S15" t="n">
-        <v>-3.9852</v>
+        <v>-4.9395</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.8129</v>
+        <v>-1.3419</v>
       </c>
       <c r="U15" t="n">
-        <v>-2.1722</v>
+        <v>-3.5976</v>
       </c>
       <c r="V15" t="n">
-        <v>-6.5835</v>
+        <v>-6.9246</v>
       </c>
       <c r="W15" t="n">
-        <v>2.0567</v>
+        <v>7.9465</v>
       </c>
       <c r="X15" t="n">
-        <v>-8.6401</v>
+        <v>-14.8711</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. POU BLINNIKOV</t>
+          <t>A. BENNASAR ROJO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,70 +1654,70 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D16" t="n">
-        <v>-32.57</v>
+        <v>-29.7711</v>
       </c>
       <c r="E16" t="n">
-        <v>-19.8903</v>
+        <v>-19.0883</v>
       </c>
       <c r="F16" t="n">
-        <v>-12.6795</v>
+        <v>-10.6822</v>
       </c>
       <c r="G16" t="n">
-        <v>-7.2502</v>
+        <v>-23.7503</v>
       </c>
       <c r="H16" t="n">
-        <v>-15.2013</v>
+        <v>-15.2129</v>
       </c>
       <c r="I16" t="n">
-        <v>7.9513</v>
+        <v>-8.5372</v>
       </c>
       <c r="J16" t="n">
-        <v>11.1473</v>
+        <v>-6.289700000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>0.4509999999999998</v>
+        <v>-4.753900000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>10.6964</v>
+        <v>-1.5355</v>
       </c>
       <c r="M16" t="n">
-        <v>-18.3974</v>
+        <v>-17.4602</v>
       </c>
       <c r="N16" t="n">
-        <v>-15.652</v>
+        <v>-10.459</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.7455</v>
+        <v>-7.0015</v>
       </c>
       <c r="P16" t="n">
-        <v>-9.1256</v>
+        <v>3.3728</v>
       </c>
       <c r="Q16" t="n">
-        <v>-34.3203</v>
+        <v>-13.8867</v>
       </c>
       <c r="R16" t="n">
-        <v>25.195</v>
+        <v>17.2595</v>
       </c>
       <c r="S16" t="n">
-        <v>-9.269399999999999</v>
+        <v>-2.81</v>
       </c>
       <c r="T16" t="n">
-        <v>-4.6636</v>
+        <v>-0.9684999999999998</v>
       </c>
       <c r="U16" t="n">
-        <v>-4.606</v>
+        <v>-1.8418</v>
       </c>
       <c r="V16" t="n">
-        <v>-6.9246</v>
+        <v>-6.5835</v>
       </c>
       <c r="W16" t="n">
-        <v>7.9465</v>
+        <v>2.0567</v>
       </c>
       <c r="X16" t="n">
-        <v>-14.8711</v>
+        <v>-8.6401</v>
       </c>
     </row>
     <row r="17">
@@ -1735,16 +1735,16 @@
         <v>26</v>
       </c>
       <c r="D17" t="n">
-        <v>-59.70220000000002</v>
+        <v>-32.3185</v>
       </c>
       <c r="E17" t="n">
-        <v>17.41979999999999</v>
+        <v>28.43220000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>-77.122</v>
+        <v>-60.7503</v>
       </c>
       <c r="G17" t="n">
-        <v>-98.3569</v>
+        <v>-98.35690000000001</v>
       </c>
       <c r="H17" t="n">
         <v>-87.378</v>
@@ -1777,19 +1777,19 @@
         <v>-380.8955</v>
       </c>
       <c r="R17" t="n">
-        <v>426.5277</v>
+        <v>426.5277000000001</v>
       </c>
       <c r="S17" t="n">
-        <v>-11.504</v>
+        <v>15.87970000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>2.771900000000004</v>
+        <v>13.7845</v>
       </c>
       <c r="U17" t="n">
-        <v>-14.2753</v>
+        <v>2.0955</v>
       </c>
       <c r="V17" t="n">
-        <v>4.530500000000002</v>
+        <v>4.530500000000013</v>
       </c>
       <c r="W17" t="n">
         <v>146.7257</v>
